--- a/파이썬/코딩교실/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 수강신청.xlsx
+++ b/파이썬/코딩교실/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 수강신청.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KJG\Documents\GitHub\enoz_kjg\파이썬\코딩교실 매크로\1.코딩교실준비\2.추가인원 수강신청\1.추가인원 가입 수강신청\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EnozAce\Documents\GitHub\enoz_kjg\파이썬\코딩교실\1.코딩교실준비\2.추가인원 수강신청\1.추가인원 가입 수강신청\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CB1784D-BAE7-438A-84FB-712507AA5B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AFFAE49-4BA5-4223-98F6-CFD0DBBBDBA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2928" yWindow="564" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
@@ -33,9 +33,10 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -51,31 +52,61 @@
   <commentList>
     <comment ref="S1" authorId="0" shapeId="0" xr:uid="{3EAFA026-55CE-416C-9329-E5960861AB96}">
       <text>
-        <t>[스레드 댓글]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="맑은 고딕"/>
+            <family val="2"/>
+            <charset val="129"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[스레드 댓글]
 사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
 댓글:
     몇 명 등록할 것인지 설정</t>
+        </r>
       </text>
     </comment>
     <comment ref="S2" authorId="1" shapeId="0" xr:uid="{BF3D0178-CC52-4324-B9A2-4653C6AB4A40}">
       <text>
-        <t>[스레드 댓글]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="맑은 고딕"/>
+            <family val="2"/>
+            <charset val="129"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[스레드 댓글]
 사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
 댓글:
     랜덤 대기시간의 최소값
 ex) 10분에서 20분사이에 반복하려면
 10x60인 600을 넣어야 함</t>
+        </r>
       </text>
     </comment>
     <comment ref="S3" authorId="2" shapeId="0" xr:uid="{FEDADFAE-7FA7-4CEB-BFA8-6509247C4F28}">
       <text>
-        <t xml:space="preserve">[스레드 댓글]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="맑은 고딕"/>
+            <family val="2"/>
+            <charset val="129"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">[스레드 댓글]
 사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
 댓글:
     랜덤 대기시간의 최소값
 ex) 10분에서 20분사이에 반복하려면
 20x60인 1200을 넣어야 함
 </t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -5581,9 +5612,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5621,7 +5652,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -5727,7 +5758,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5869,7 +5900,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5900,25 +5931,25 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:X501"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="17.19921875" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="48.59765625" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="11.3984375" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="17.25" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="48.625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="11.375" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="0" style="2" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="10.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.59765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.625" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.69921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.75" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="9" style="2"/>
-    <col min="11" max="12" width="10.59765625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="8.69921875"/>
+    <col min="11" max="12" width="10.625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="8.75"/>
     <col min="14" max="14" width="9" style="2"/>
-    <col min="15" max="16" width="10.59765625" style="2" customWidth="1"/>
-    <col min="17" max="17" width="8.69921875"/>
+    <col min="15" max="16" width="10.625" style="2" customWidth="1"/>
+    <col min="17" max="17" width="8.75"/>
     <col min="18" max="18" width="9" style="2"/>
-    <col min="19" max="19" width="20.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="48.3984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="48.375" style="2" bestFit="1" customWidth="1"/>
     <col min="21" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -5952,7 +5983,7 @@
         <v>1263</v>
       </c>
       <c r="T1" s="2">
-        <v>3</v>
+        <v>200</v>
       </c>
       <c r="V1"/>
       <c r="W1"/>
@@ -6451,7 +6482,7 @@
       <c r="T17" s="25"/>
       <c r="U17" s="26"/>
     </row>
-    <row r="18" spans="1:21" ht="19.2">
+    <row r="18" spans="1:21" ht="17.25">
       <c r="A18" s="2"/>
       <c r="B18" s="15"/>
       <c r="C18" s="2"/>
@@ -6559,7 +6590,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="22" spans="1:21" ht="19.2">
+    <row r="22" spans="1:21" ht="17.25">
       <c r="A22" s="2"/>
       <c r="B22" s="16"/>
       <c r="C22" s="2"/>
@@ -11558,17 +11589,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E1EB988-2ED1-436F-8BF0-F3686DC619B0}">
   <dimension ref="A1:T127"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="17.19921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="48.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="2"/>
     <col min="5" max="16" width="9" style="2" hidden="1" customWidth="1"/>
     <col min="17" max="17" width="0" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="9" style="2"/>
-    <col min="19" max="19" width="12.3984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="48.3984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="48.375" style="2" bestFit="1" customWidth="1"/>
     <col min="21" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -13006,14 +13037,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{801651D1-1060-4046-8C27-A9334BE84870}">
   <dimension ref="A1:T63"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="17.19921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="54.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="54.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.375" bestFit="1" customWidth="1"/>
     <col min="5" max="16" width="0" hidden="1" customWidth="1"/>
-    <col min="19" max="19" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="48.3984375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="48.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
@@ -13094,7 +13125,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="19.2">
+    <row r="7" spans="1:20" ht="17.25">
       <c r="A7" s="7" t="s">
         <v>14</v>
       </c>
@@ -13138,7 +13169,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="19.2">
+    <row r="11" spans="1:20" ht="17.25">
       <c r="A11" s="7" t="s">
         <v>5</v>
       </c>
@@ -13160,7 +13191,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="19.2">
+    <row r="13" spans="1:20" ht="17.25">
       <c r="A13" s="7" t="s">
         <v>5</v>
       </c>
@@ -13435,7 +13466,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="19.2">
+    <row r="38" spans="1:3" ht="17.25">
       <c r="A38" s="7" t="s">
         <v>1298</v>
       </c>
@@ -13479,7 +13510,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="19.2">
+    <row r="42" spans="1:3" ht="17.25">
       <c r="A42" s="7" t="s">
         <v>1299</v>
       </c>
@@ -13632,9 +13663,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ECF04CD-0782-4755-8611-A09CA217F0DE}">
   <dimension ref="A1:D166"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="2" max="2" width="17.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -15259,7 +15290,7 @@
         <v>1331</v>
       </c>
     </row>
-    <row r="136" spans="1:4" ht="19.2">
+    <row r="136" spans="1:4" ht="17.25">
       <c r="A136" s="30"/>
       <c r="B136" s="1" t="s">
         <v>1271</v>
